--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -273,8 +273,8 @@
     <t>物質には、個人に適切な投与量で正しく投与される治療物質が含まれますが、これらに限定されません。食物;植物または動物に由来する材料。または昆虫の刺し傷からの毒。 / Substances include, but are not limited to: a therapeutic substance administered correctly at an appropriate dosage for the individual; food; material derived from plants or animals; or venom from insect stings.</t>
   </si>
   <si>
-    <t>ait-1:AllergyIntolerance.ClinicalStatusが存在する場合は、存在するものとします。 / AllergyIntolerance.clinicalStatus SHALL be present if verificationStatus is not entered-in-error. {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').exists() or clinicalStatus.exists()}
-ait-2:AllergyIntolerance.ClinicalStatusは、検証ステータスが入力されている場合、存在しないでください / AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').empty() or clinicalStatus.empty()}dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>ait-1:AllergyIntolerance.verificationStatusに'entered-in-error'が入力されていない場合には、AllergyIntolerance.ClinicalStatusは、存在しなければならない。/ AllergyIntolerance.clinicalStatus SHALL be present if verificationStatus is not entered-in-error. {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').exists() or clinicalStatus.exists()}
+ait-2:AllergyIntolerance.verificationStatusに'entered-in-error'が入力されている場合、AllergyIntolerance.ClinicalStatusは、存在してはならない。 / AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').empty() or clinicalStatus.empty()}dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照しなければならない。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはあってはならない。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
@@ -312,16 +312,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -447,7 +447,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -478,10 +478,10 @@
     <t>このアイテムの外部ID / External ids for this item</t>
   </si>
   <si>
-    <t>リソースが更新され、サーバーからサーバーに伝播するにつれて一定のままであるパフォーマーまたは他のシステムによってこのアレルギー耐性に割り当てられたビジネス識別子。 / Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません（[ディスカッション]（Resource.html＃識別子を参照））。識別子が単一のリソースインスタンスにのみ表示することがベストプラクティスですが、ビジネス慣行は、同じ識別子を持つ複数のリソースインスタンスが存在する可能性があることを時々決定する場合があります。たとえば、複数の患者と個人のリソースインスタンスは、同じ社会保険番号を共有する場合があります。 / This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>リソースが更新され、サーバーからサーバーに伝播するにつれて一定のままであるパフォーマーまたは他のシステムによってこのアレルギー耐性に割り当てられたビジネスidentifier。 / Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません（[ディスカッション]（Resource.html＃identifierを参照））。identifierが単一のリソースインスタンスにのみ表示することがベストプラクティスですが、ビジネス慣行は、同じidentifierを持つ複数のリソースインスタンスが存在する可能性があることを時々決定する場合があります。たとえば、複数の患者と個人のリソースインスタンスは、同じ社会保険番号を共有する場合があります。 / This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
   </si>
   <si>
     <t>さまざまな参加システムで知られており、サーバー全体で一貫している方法でアレルギー耐性を識別できるようにします。 / Allows identification of the AllergyIntolerance as it is known by various participating systems and in a way that remains consistent across servers.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -274,7 +274,7 @@
   </si>
   <si>
     <t>ait-1:AllergyIntolerance.verificationStatusに'entered-in-error'が入力されていない場合には、AllergyIntolerance.ClinicalStatusは、存在しなければならない。/ AllergyIntolerance.clinicalStatus SHALL be present if verificationStatus is not entered-in-error. {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').exists() or clinicalStatus.exists()}
-ait-2:AllergyIntolerance.verificationStatusに'entered-in-error'が入力されている場合、AllergyIntolerance.ClinicalStatusは、存在してはならない。 / AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').empty() or clinicalStatus.empty()}dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照しなければならない。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはあってはならない。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+ait-2:AllergyIntolerance.verificationStatusに'entered-in-error'が入力されている場合、AllergyIntolerance.ClinicalStatusは、存在してはならない。 / AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system = 'http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code = 'entered-in-error').empty() or clinicalStatus.empty()}dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照しなければならない。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはあってはならない。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Observation[classCode=OBS, moodCode=EVN]</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -263,11 +263,11 @@
 </t>
   </si>
   <si>
-    <t>Allergy or Intolerance (generally: Risk of adverse reaction to a substance). アレルギー不耐症 (特定の物質への暴露で生じた有害反応)</t>
+    <t>Allergy or Intolerance (generally: Risk of adverse reaction to a substance). アレルギー不耐症 (特定の物質への曝露で生じた有害反応)</t>
   </si>
   <si>
     <t>Risk of harmful or undesirable, physiological response which is unique to an individual and associated with exposure to a substance.  
-このリソースは患者のアレルギー不耐症を表現する。具体的には、特定の物質または物質群への暴露によって生じる有害反応の傾向や、潜在的なリスクを表現する。</t>
+このリソースは患者のアレルギー不耐症を表現する。具体的には、特定の物質または物質群へのに曝露よって生じる有害反応の傾向や、潜在的なリスクを表現する。</t>
   </si>
   <si>
     <t>物質には、個人に適切な投与量で正しく投与される治療物質が含まれますが、これらに限定されません。食物;植物または動物に由来する材料。または昆虫の刺し傷からの毒。 / Substances include, but are not limited to: a therapeutic substance administered correctly at an appropriate dosage for the individual; food; material derived from plants or animals; or venom from insect stings.</t>
@@ -880,11 +880,11 @@
 </t>
   </si>
   <si>
-    <t>Adverse Reaction Events linked to exposure to substance. このアレルゲンへの暴露に関連する有害反応</t>
+    <t>Adverse Reaction Events linked to exposure to substance. このアレルゲンへの曝露に関連する有害反応</t>
   </si>
   <si>
     <t>Details about each adverse reaction event linked to exposure to the identified substance.  
-同定された物質への暴露に関連する個々の有害反応に関する詳細情報。</t>
+同定された物質への曝露に関連する個々の有害反応に関する詳細情報。</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SUBJ].target[classCode=OBS, moodCode=EVN, code &lt;= CommonClinicalObservationType, value &lt;= ObservationValue (Reaction Type)]</t>
@@ -1042,11 +1042,11 @@
     <t>AllergyIntolerance.reaction.exposureRoute</t>
   </si>
   <si>
-    <t>How the subject was exposed to the substance. 患者がこの物質にどのように暴露したか</t>
+    <t>How the subject was exposed to the substance. 患者がこの物質にどのように曝露したか</t>
   </si>
   <si>
     <t>Identification of the route by which the subject was exposed to the substance.  
-患者がどのような経路でこの物質に暴露したかの同定。</t>
+患者がどのような経路でこの物質に曝露したかの同定。</t>
   </si>
   <si>
     <t>可能な限り、用語による露出経路のコーディングは、可能な限り使用する必要があります。 / Coding of the route of exposure with a terminology should be used wherever possible.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -748,11 +748,11 @@
 AgePeriodRangestring</t>
   </si>
   <si>
-    <t>When allergy or intolerance was identified. このアレルギー不耐症のオンセット</t>
+    <t>When allergy or intolerance was identified. アレルギー不耐症が出現した時期</t>
   </si>
   <si>
     <t>Estimated or actual date, date-time, or age when allergy or intolerance was identified.  
-このアレルギー不耐症が同定された事実もしくは推定された時期（日付、日時、年齢）。</t>
+このアレルギー不耐症が確認された、もしくは推定された時期（日付、日時、年齢）</t>
   </si>
   <si>
     <t>effectiveTime.low</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -1378,17 +1378,17 @@
   <dimension ref="A1:AM36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.9609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.9609375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="185.2109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="158.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1397,25 +1397,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="179.01953125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="40.39453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="153.4765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.62109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="34.6328125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.265625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="34.51953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -366,7 +366,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -955,7 +955,7 @@
     <t>物質のタイプを定義するコード（医薬品を含む）。 / Codes defining the type of the substance (including pharmaceutical products).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/substance-code</t>
+    <t>http://hl7.org/fhir/ValueSet/substance-code|4.0.1</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].participation[typeCode=CSM].role[classCode=ADMM].player[classCode=MAT, determinerCode=KIND, code &lt;= ExposureAgentEntityType]</t>
@@ -981,7 +981,7 @@
     <t>有害反応イベントに観察または関連する臨床症状および/または徴候。 / Clinical symptoms and/or signs that are observed or associated with an Adverse Reaction Event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>AL1-5</t>
@@ -1055,7 +1055,7 @@
     <t>被験者の体への、またはそれへの治療剤の投与の経路または生理学的経路を説明するコード化された概念。 / A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].routeCode</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
